--- a/Table/UnitWeaponTable.xlsx
+++ b/Table/UnitWeaponTable.xlsx
@@ -69,23 +69,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponType-int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Path-string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>권총</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pistal02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -125,6 +109,22 @@
   </si>
   <si>
     <t>Speed-int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Category-string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Label-string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pistal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -518,16 +518,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -535,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1">
         <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -555,13 +555,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <v>32</v>
@@ -639,27 +639,27 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
